--- a/src/test/resources/accountln_information.xlsx
+++ b/src/test/resources/accountln_information.xlsx
@@ -27,39 +27,72 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
-  <si>
-    <t>Fullname</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
+  <si>
+    <t>FullName</t>
   </si>
   <si>
     <t>Birthday</t>
   </si>
   <si>
+    <t>Phone</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
     <t>Address</t>
   </si>
   <si>
-    <t>Nguyen Van A</t>
-  </si>
-  <si>
-    <t>123 Nguyen Trai, P.5, Q.1, TP. Ho Chi Minh</t>
-  </si>
-  <si>
-    <t>Tran Thi B</t>
-  </si>
-  <si>
-    <t>456 Le Loi, P.10, Q.3, TP. Ho Chi Minh</t>
-  </si>
-  <si>
-    <t>Le Van C</t>
-  </si>
-  <si>
-    <t>789 Tran Phu, P.15, Q.5, TP. Da Nang</t>
-  </si>
-  <si>
-    <t>Pham Hong D</t>
-  </si>
-  <si>
-    <t>101 Hai Ba Trung, P.2, Q.1, TP. Ha Noi</t>
+    <t>Note</t>
+  </si>
+  <si>
+    <t>Nguyễn Văn A</t>
+  </si>
+  <si>
+    <t>15/08/1995</t>
+  </si>
+  <si>
+    <t>0987770202</t>
+  </si>
+  <si>
+    <t>NguyenVanA@gmail.com</t>
+  </si>
+  <si>
+    <t>123 Đường ABC, Quận 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thông tin hợp lệ </t>
+  </si>
+  <si>
+    <t>Kiểm tra cập nhật ngày sinh thành công</t>
+  </si>
+  <si>
+    <t>Kiểm tra cập nhật số điện thoại thành công</t>
+  </si>
+  <si>
+    <t>test@gmail.com</t>
+  </si>
+  <si>
+    <t>Kiểm tra cập nhật email thành công</t>
+  </si>
+  <si>
+    <t>Trần Thị B</t>
+  </si>
+  <si>
+    <t>20/12/1990</t>
+  </si>
+  <si>
+    <t>newemail@gmail.com</t>
+  </si>
+  <si>
+    <t>Kiểm tra cập nhật toàn bộ 5 trường</t>
+  </si>
+  <si>
+    <t>456 Đường DEF, Quận 3</t>
+  </si>
+  <si>
+    <t>Kiểm tra cập nhật địa chỉ thành công</t>
   </si>
 </sst>
 </file>
@@ -72,8 +105,16 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
-    <font>
+  <fonts count="21">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -545,142 +586,151 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="58" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" quotePrefix="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1215,68 +1265,135 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="4" outlineLevelCol="2"/>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="7" outlineLevelCol="5"/>
   <cols>
     <col min="2" max="2" width="14.1111111111111" customWidth="1"/>
+    <col min="3" max="3" width="10.6666666666667"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="1">
-        <v>32874</v>
-      </c>
-      <c r="C2" t="s">
-        <v>4</v>
+    <row r="2" ht="57.6" spans="1:6">
+      <c r="A2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="1">
-        <v>33736</v>
-      </c>
-      <c r="C3" t="s">
-        <v>6</v>
+    <row r="3" ht="72" spans="1:6">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="1">
-        <v>31251</v>
-      </c>
-      <c r="C4" t="s">
-        <v>8</v>
+    <row r="4" ht="86.4" spans="1:6">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2">
+        <v>987654321</v>
+      </c>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="1">
-        <v>36799</v>
-      </c>
-      <c r="C5" t="s">
+    <row r="5" ht="72" spans="1:6">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" ht="57.6" spans="1:6">
+      <c r="A6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="2">
+        <v>912345678</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>10</v>
       </c>
+      <c r="F6" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" ht="72" spans="1:6">
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D5" r:id="rId1" display="test@gmail.com" tooltip="mailto:test@gmail.com"/>
+    <hyperlink ref="D6" r:id="rId2" display="newemail@gmail.com" tooltip="mailto:newemail@gmail.com"/>
+    <hyperlink ref="D2" r:id="rId3" display="NguyenVanA@gmail.com"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
